--- a/output/pdf_financials_xlsx/XPLR.xlsx
+++ b/output/pdf_financials_xlsx/XPLR.xlsx
@@ -3358,25 +3358,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.08000699999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.08000699999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.0876</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.010081</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.274299</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.249276</v>
       </c>
     </row>
     <row r="93">
@@ -4152,13 +4152,13 @@
         <v>-0.348253</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.313222</v>
+        <v>0.21593</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1.111618</v>
+        <v>0.237197</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.645628</v>
+        <v>0.41801</v>
       </c>
     </row>
     <row r="119">
@@ -5424,7 +5424,11 @@
           <t>Share-based payments reserve (note 12)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -5908,7 +5912,11 @@
           <t>Share-based Payments Reserve (note 12)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -6464,7 +6472,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -6828,7 +6840,11 @@
           <t>Share-based payments reserve 8</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -7154,7 +7170,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -7656,7 +7676,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -8680,7 +8704,11 @@
           <t>Deposits used for exploration and evaluation asset expenditures $</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XPLR.xlsx
+++ b/output/pdf_financials_xlsx/XPLR.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001125</v>
       </c>
     </row>
     <row r="13">
@@ -1285,7 +1285,7 @@
         <v>-1.83615</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.399908</v>
+        <v>-1.401033</v>
       </c>
     </row>
     <row r="28">
@@ -1347,7 +1347,7 @@
         <v>-1.83615</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.399908</v>
+        <v>-1.401033</v>
       </c>
     </row>
     <row r="30">
@@ -1489,28 +1489,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06882199999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.277415</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.245702</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.723189</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.30271</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.053485</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.435621</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.003876</v>
       </c>
     </row>
     <row r="35">
@@ -1551,28 +1551,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.06882199999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.277415</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.245702</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.723189</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.30271</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.053485</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.435621</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.003876</v>
       </c>
     </row>
     <row r="37">
@@ -1932,19 +1932,19 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.772522</v>
+        <v>0.049333</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.334175</v>
+        <v>0.031465</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.105285</v>
+        <v>0.0518</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.668741</v>
+        <v>0.23312</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.538601</v>
+        <v>0.534725</v>
       </c>
     </row>
     <row r="49">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">

--- a/output/pdf_financials_xlsx/XPLR.xlsx
+++ b/output/pdf_financials_xlsx/XPLR.xlsx
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="10">
@@ -11692,7 +11692,11 @@
           <t>Occupancy cost (note 10)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -13080,7 +13084,11 @@
           <t>Occupancy cost</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XPLR.xlsx
+++ b/output/pdf_financials_xlsx/XPLR.xlsx
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001005</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002386</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.001946</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.025391</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.018278</v>
+        <v>0.017273</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.010237</v>
+        <v>-0.012623</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>3.5e-05</v>
+        <v>0.001981</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.146208</v>
@@ -11010,7 +11010,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E113" s="5" t="n">
         <v>-0.001005</v>
       </c>
@@ -11118,7 +11122,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>0.1</v>
       </c>
